--- a/output/roomself_excel/5965.xlsx
+++ b/output/roomself_excel/5965.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>210022</v>
+        <v>135318</v>
       </c>
       <c r="D2" t="n">
-        <v>4663</v>
+        <v>3304</v>
       </c>
       <c r="E2" t="n">
-        <v>903</v>
+        <v>470</v>
       </c>
       <c r="F2" t="n">
-        <v>887</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>43186</v>
+        <v>324940</v>
       </c>
       <c r="D3" t="n">
-        <v>1780</v>
+        <v>6800</v>
       </c>
       <c r="E3" t="n">
-        <v>180</v>
+        <v>911</v>
       </c>
       <c r="F3" t="n">
-        <v>163</v>
+        <v>905</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9240</v>
+        <v>90563</v>
       </c>
       <c r="D4" t="n">
-        <v>828</v>
+        <v>2412</v>
       </c>
       <c r="E4" t="n">
-        <v>158</v>
+        <v>290</v>
       </c>
       <c r="F4" t="n">
-        <v>120</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>158820</v>
+        <v>115806</v>
       </c>
       <c r="D5" t="n">
-        <v>5500</v>
+        <v>3516</v>
       </c>
       <c r="E5" t="n">
-        <v>567</v>
+        <v>1085</v>
       </c>
       <c r="F5" t="n">
-        <v>254</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>553537</v>
+        <v>113243</v>
       </c>
       <c r="D6" t="n">
-        <v>11604</v>
+        <v>2904</v>
       </c>
       <c r="E6" t="n">
-        <v>912</v>
+        <v>419</v>
       </c>
       <c r="F6" t="n">
-        <v>905</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>90563</v>
+        <v>9240</v>
       </c>
       <c r="D7" t="n">
-        <v>2412</v>
+        <v>828</v>
       </c>
       <c r="E7" t="n">
-        <v>290</v>
+        <v>158</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>91124</v>
+        <v>67469</v>
       </c>
       <c r="D8" t="n">
-        <v>2544</v>
+        <v>2568</v>
       </c>
       <c r="E8" t="n">
-        <v>450</v>
+        <v>331</v>
       </c>
       <c r="F8" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>234273</v>
+        <v>29766</v>
       </c>
       <c r="D9" t="n">
-        <v>4708</v>
+        <v>1460</v>
       </c>
       <c r="E9" t="n">
-        <v>628</v>
+        <v>177</v>
       </c>
       <c r="F9" t="n">
-        <v>458</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14208</v>
+        <v>81931</v>
       </c>
       <c r="D10" t="n">
-        <v>956</v>
+        <v>2668</v>
       </c>
       <c r="E10" t="n">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>115806</v>
+        <v>45280</v>
       </c>
       <c r="D11" t="n">
-        <v>3516</v>
+        <v>1772</v>
       </c>
       <c r="E11" t="n">
-        <v>700</v>
+        <v>283</v>
       </c>
       <c r="F11" t="n">
-        <v>318</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30752</v>
+        <v>91124</v>
       </c>
       <c r="D12" t="n">
-        <v>1456</v>
+        <v>2544</v>
       </c>
       <c r="E12" t="n">
-        <v>228</v>
+        <v>450</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>272159</v>
+        <v>14208</v>
       </c>
       <c r="D13" t="n">
-        <v>4624</v>
+        <v>956</v>
       </c>
       <c r="E13" t="n">
-        <v>752</v>
+        <v>350</v>
       </c>
       <c r="F13" t="n">
-        <v>537</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>68249</v>
+        <v>47273</v>
       </c>
       <c r="D14" t="n">
-        <v>2323</v>
+        <v>2012</v>
       </c>
       <c r="E14" t="n">
-        <v>358</v>
+        <v>237</v>
       </c>
       <c r="F14" t="n">
-        <v>330</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>29766</v>
+        <v>11102</v>
       </c>
       <c r="D15" t="n">
-        <v>1460</v>
+        <v>852</v>
       </c>
       <c r="E15" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>310096</v>
+        <v>68249</v>
       </c>
       <c r="D16" t="n">
-        <v>6428</v>
+        <v>2323</v>
       </c>
       <c r="E16" t="n">
-        <v>841</v>
+        <v>358</v>
       </c>
       <c r="F16" t="n">
-        <v>448</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>113243</v>
+        <v>246</v>
       </c>
       <c r="D17" t="n">
-        <v>2904</v>
+        <v>500</v>
       </c>
       <c r="E17" t="n">
-        <v>419</v>
+        <v>470</v>
       </c>
       <c r="F17" t="n">
-        <v>369</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,152 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>45280</v>
+        <v>210022</v>
       </c>
       <c r="D18" t="n">
-        <v>1772</v>
+        <v>4663</v>
       </c>
       <c r="E18" t="n">
-        <v>283</v>
+        <v>903</v>
       </c>
       <c r="F18" t="n">
-        <v>32</v>
+        <v>887</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>43186</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1780</v>
+      </c>
+      <c r="E19" t="n">
+        <v>180</v>
+      </c>
+      <c r="F19" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>44078</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1708</v>
+      </c>
+      <c r="E20" t="n">
+        <v>223</v>
+      </c>
+      <c r="F20" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>234273</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4708</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1151</v>
+      </c>
+      <c r="F21" t="n">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>30752</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1456</v>
+      </c>
+      <c r="E22" t="n">
+        <v>651</v>
+      </c>
+      <c r="F22" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>272159</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4624</v>
+      </c>
+      <c r="E23" t="n">
+        <v>898</v>
+      </c>
+      <c r="F23" t="n">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>310096</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6428</v>
+      </c>
+      <c r="E24" t="n">
+        <v>898</v>
+      </c>
+      <c r="F24" t="n">
+        <v>841</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/5965.xlsx
+++ b/output/roomself_excel/5965.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:AE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,137 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_7</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_7</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_8</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_8</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_8</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_9</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_9</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_9</t>
         </is>
       </c>
     </row>
@@ -475,12 +600,41 @@
       <c r="D2" t="n">
         <v>3304</v>
       </c>
-      <c r="E2" t="n">
-        <v>470</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>327</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +651,49 @@
       <c r="D3" t="n">
         <v>6800</v>
       </c>
-      <c r="E3" t="n">
-        <v>911</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>905</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="G3" t="n">
+        <v>32</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>789</v>
+      </c>
+      <c r="J3" t="n">
+        <v>32</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +710,41 @@
       <c r="D4" t="n">
         <v>2412</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>290</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>33</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +761,41 @@
       <c r="D5" t="n">
         <v>3516</v>
       </c>
-      <c r="E5" t="n">
-        <v>1085</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>318</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +812,49 @@
       <c r="D6" t="n">
         <v>2904</v>
       </c>
-      <c r="E6" t="n">
-        <v>419</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>369</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>389</v>
+      </c>
+      <c r="J6" t="n">
+        <v>32</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +871,49 @@
       <c r="D7" t="n">
         <v>828</v>
       </c>
-      <c r="E7" t="n">
-        <v>158</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>120</v>
       </c>
+      <c r="G7" t="n">
+        <v>33</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>87</v>
+      </c>
+      <c r="J7" t="n">
+        <v>38</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +930,49 @@
       <c r="D8" t="n">
         <v>2568</v>
       </c>
-      <c r="E8" t="n">
-        <v>331</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>254</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="G8" t="n">
+        <v>33</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>108</v>
+      </c>
+      <c r="J8" t="n">
+        <v>38</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +989,33 @@
       <c r="D9" t="n">
         <v>1460</v>
       </c>
-      <c r="E9" t="n">
-        <v>177</v>
-      </c>
-      <c r="F9" t="n">
-        <v>16</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +1032,33 @@
       <c r="D10" t="n">
         <v>2668</v>
       </c>
-      <c r="E10" t="n">
-        <v>328</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +1075,41 @@
       <c r="D11" t="n">
         <v>1772</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>283</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>32</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +1126,49 @@
       <c r="D12" t="n">
         <v>2544</v>
       </c>
-      <c r="E12" t="n">
-        <v>450</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>249</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="G12" t="n">
+        <v>32</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>418</v>
+      </c>
+      <c r="J12" t="n">
+        <v>31</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +1185,33 @@
       <c r="D13" t="n">
         <v>956</v>
       </c>
-      <c r="E13" t="n">
-        <v>350</v>
-      </c>
-      <c r="F13" t="n">
-        <v>11</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1228,33 @@
       <c r="D14" t="n">
         <v>2012</v>
       </c>
-      <c r="E14" t="n">
-        <v>237</v>
-      </c>
-      <c r="F14" t="n">
-        <v>13</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1271,33 @@
       <c r="D15" t="n">
         <v>852</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,11 +1314,104 @@
       <c r="D16" t="n">
         <v>2323</v>
       </c>
-      <c r="E16" t="n">
-        <v>358</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>330</v>
+        <v>175</v>
+      </c>
+      <c r="G16" t="n">
+        <v>26</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>59</v>
+      </c>
+      <c r="J16" t="n">
+        <v>27</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>191</v>
+      </c>
+      <c r="M16" t="n">
+        <v>22</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>189</v>
+      </c>
+      <c r="P16" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>98</v>
+      </c>
+      <c r="S16" t="n">
+        <v>26</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>41</v>
+      </c>
+      <c r="V16" t="n">
+        <v>28</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
+        <v>126</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -805,12 +1429,33 @@
       <c r="D17" t="n">
         <v>500</v>
       </c>
-      <c r="E17" t="n">
-        <v>470</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1472,41 @@
       <c r="D18" t="n">
         <v>4663</v>
       </c>
-      <c r="E18" t="n">
-        <v>903</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>887</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1523,49 @@
       <c r="D19" t="n">
         <v>1780</v>
       </c>
-      <c r="E19" t="n">
-        <v>180</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>163</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="G19" t="n">
+        <v>21</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>159</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1582,41 @@
       <c r="D20" t="n">
         <v>1708</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>223</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>33</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1633,49 @@
       <c r="D21" t="n">
         <v>4708</v>
       </c>
-      <c r="E21" t="n">
-        <v>1151</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>898</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="G21" t="n">
+        <v>32</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>313</v>
+      </c>
+      <c r="J21" t="n">
+        <v>30</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1692,41 @@
       <c r="D22" t="n">
         <v>1456</v>
       </c>
-      <c r="E22" t="n">
-        <v>651</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>91</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="G22" t="n">
+        <v>38</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1743,65 @@
       <c r="D23" t="n">
         <v>4624</v>
       </c>
-      <c r="E23" t="n">
-        <v>898</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>752</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>373</v>
+      </c>
+      <c r="J23" t="n">
+        <v>25</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>398</v>
+      </c>
+      <c r="M23" t="n">
+        <v>27</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>658</v>
+      </c>
+      <c r="P23" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1818,73 @@
       <c r="D24" t="n">
         <v>6428</v>
       </c>
-      <c r="E24" t="n">
-        <v>898</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>841</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="G24" t="n">
+        <v>26</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>198</v>
+      </c>
+      <c r="J24" t="n">
+        <v>30</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>16</v>
+      </c>
+      <c r="M24" t="n">
+        <v>15</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>192</v>
+      </c>
+      <c r="P24" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>794</v>
+      </c>
+      <c r="S24" t="n">
+        <v>32</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/5965.xlsx
+++ b/output/roomself_excel/5965.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE24"/>
+  <dimension ref="A1:AU24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,6 +582,86 @@
       <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_9</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
         </is>
       </c>
     </row>
@@ -635,6 +715,46 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>77</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>172</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>33</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -694,6 +814,70 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>74</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>255</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>421</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>76</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -745,6 +929,34 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>175</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -796,6 +1008,22 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -855,6 +1083,34 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>161</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -914,6 +1170,34 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>87</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -973,6 +1257,58 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>159</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1016,6 +1352,22 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1059,6 +1411,22 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1110,6 +1478,46 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>71</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>76</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1169,6 +1577,22 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1212,6 +1636,22 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1255,6 +1695,22 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1298,6 +1754,22 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1413,6 +1885,58 @@
       <c r="AE16" t="n">
         <v>32</v>
       </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AL16" t="n">
+        <v>31</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AP16" t="n">
+        <v>74</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1456,6 +1980,22 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1507,6 +2047,22 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1566,6 +2122,34 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1617,6 +2201,34 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>77</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1676,6 +2288,22 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1727,6 +2355,34 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>190</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1802,6 +2458,22 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1885,6 +2557,22 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
